--- a/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T16:07:27+00:00</t>
+    <t>2026-08-31T20:29:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:29:59+00:00</t>
+    <t>2026-09-01T08:25:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:25:15+00:00</t>
+    <t>2026-09-01T09:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:40:46+00:00</t>
+    <t>2026-09-01T10:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T10:03:55+00:00</t>
+    <t>2026-09-01T13:17:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:17:32+00:00</t>
+    <t>2026-09-03T11:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2683" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2683" uniqueCount="522">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:23:31+00:00</t>
+    <t>2026-09-03T16:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -896,6 +896,12 @@
   </si>
   <si>
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
+  &lt;code value="276031006"/&gt;
+&lt;/valueCoding&gt;</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -5440,7 +5446,7 @@
         <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>82</v>
@@ -5479,7 +5485,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5500,10 +5506,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5514,10 +5520,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5543,16 +5549,16 @@
         <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5601,7 +5607,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5622,10 +5628,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5636,10 +5642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5662,19 +5668,19 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5723,7 +5729,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5738,19 +5744,19 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5758,10 +5764,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5784,16 +5790,16 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5843,7 +5849,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5867,10 +5873,10 @@
         <v>269</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5878,14 +5884,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5904,19 +5910,19 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5965,7 +5971,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5980,19 +5986,19 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -6000,14 +6006,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6026,19 +6032,19 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6087,7 +6093,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6102,19 +6108,19 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6122,10 +6128,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6151,13 +6157,13 @@
         <v>129</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6207,7 +6213,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6228,13 +6234,13 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6242,10 +6248,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6268,17 +6274,17 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6327,7 +6333,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6342,19 +6348,19 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6362,10 +6368,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6391,16 +6397,16 @@
         <v>243</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6429,7 +6435,7 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6447,7 +6453,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6456,7 +6462,7 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -6465,27 +6471,27 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6600,10 +6606,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6720,10 +6726,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6807,7 +6813,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6828,10 +6834,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6842,10 +6848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6871,16 +6877,16 @@
         <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6929,7 +6935,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6950,10 +6956,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6964,10 +6970,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6993,16 +6999,16 @@
         <v>243</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7030,10 +7036,10 @@
         <v>151</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7051,7 +7057,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7060,7 +7066,7 @@
         <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>105</v>
@@ -7075,7 +7081,7 @@
         <v>192</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7086,14 +7092,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7115,16 +7121,16 @@
         <v>243</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7152,10 +7158,10 @@
         <v>151</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7173,7 +7179,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7191,27 +7197,27 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7234,19 +7240,19 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7295,7 +7301,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7316,10 +7322,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7330,10 +7336,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7359,13 +7365,13 @@
         <v>243</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7394,10 +7400,10 @@
         <v>159</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7415,7 +7421,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7433,27 +7439,27 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7479,16 +7485,16 @@
         <v>243</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7516,10 +7522,10 @@
         <v>159</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7537,7 +7543,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7558,10 +7564,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7572,10 +7578,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7598,16 +7604,16 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7657,7 +7663,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7675,27 +7681,27 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7718,16 +7724,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7777,7 +7783,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7795,27 +7801,27 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7838,19 +7844,19 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7899,7 +7905,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7911,7 +7917,7 @@
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -7920,10 +7926,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7934,10 +7940,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8052,10 +8058,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8172,14 +8178,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8201,10 +8207,10 @@
         <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>117</v>
@@ -8259,7 +8265,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8294,10 +8300,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8320,13 +8326,13 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8377,7 +8383,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8386,7 +8392,7 @@
         <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
@@ -8398,10 +8404,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8412,10 +8418,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8438,13 +8444,13 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8495,7 +8501,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8504,7 +8510,7 @@
         <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>105</v>
@@ -8516,10 +8522,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8530,10 +8536,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8559,16 +8565,16 @@
         <v>243</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8596,10 +8602,10 @@
         <v>173</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8617,7 +8623,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8635,13 +8641,13 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8652,10 +8658,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8681,16 +8687,16 @@
         <v>243</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8718,10 +8724,10 @@
         <v>159</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8739,7 +8745,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8757,13 +8763,13 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8774,10 +8780,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8800,17 +8806,17 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8859,7 +8865,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8883,7 +8889,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8894,10 +8900,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8923,10 +8929,10 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8977,7 +8983,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8998,10 +9004,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9012,10 +9018,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9038,16 +9044,16 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9097,7 +9103,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9118,10 +9124,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9132,10 +9138,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9158,16 +9164,16 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9217,7 +9223,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9238,10 +9244,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9252,10 +9258,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9278,19 +9284,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9339,7 +9345,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9360,10 +9366,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9374,10 +9380,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9492,10 +9498,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9612,14 +9618,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9641,10 +9647,10 @@
         <v>114</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>117</v>
@@ -9699,7 +9705,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9734,10 +9740,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9763,13 +9769,13 @@
         <v>243</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>264</v>
@@ -9821,7 +9827,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>93</v>
@@ -9839,7 +9845,7 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>269</v>
@@ -9856,10 +9862,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9882,19 +9888,19 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -9943,7 +9949,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9961,27 +9967,27 @@
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10007,16 +10013,16 @@
         <v>243</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10044,10 +10050,10 @@
         <v>151</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10065,7 +10071,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10074,7 +10080,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10089,7 +10095,7 @@
         <v>192</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10100,14 +10106,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10129,16 +10135,16 @@
         <v>243</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10166,10 +10172,10 @@
         <v>151</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10187,7 +10193,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10205,27 +10211,27 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10251,16 +10257,16 @@
         <v>83</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10309,7 +10315,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10330,10 +10336,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T16:19:13+00:00</t>
+    <t>2026-09-08T13:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schulabschluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T13:04:20+00:00</t>
+    <t>2026-09-08T13:56:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
